--- a/data/trans_orig/IP38F_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP38F_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>72,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>73,72%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4399</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>69,99%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>13</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1886</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26871</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23324</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28173</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29570</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25707</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31575</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>78,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>54175</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53486</t>
+          <t>49937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>56610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3194</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1189</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7057</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28173</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28173</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28173</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32764</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32764</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>32764</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4751</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8301</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40269</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36010</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41558</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37450</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33489</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40057</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>70902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5859</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8389</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
